--- a/ig/nr-corrections/StructureDefinition-as-practitioner.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21113" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21113" uniqueCount="1171">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:20:08+00:00</t>
+    <t>2024-02-12T14:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2777,426 +2777,424 @@
     <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession</t>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>profession : exercice professionnel ou future profession de l'étudiant et la catégorie de profession.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
+  </si>
+  <si>
+    <t>categorieProfession</t>
+  </si>
+  <si>
+    <t>Catégorie professionnelle indiquant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:profession</t>
   </si>
   <si>
     <t>profession</t>
   </si>
   <si>
-    <t>profession : Profession exercée ou future profession de l'étudiant.
-categorieProfessionnelle : Indique si le professionnel exerce sa profession en tant que :
-M: Militaire
-C: Civil
-F: Fonctionnaire
-E: Etudiant</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:categorieProfession</t>
-  </si>
-  <si>
-    <t>categorieProfession</t>
-  </si>
-  <si>
-    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:profession</t>
-  </si>
-  <si>
     <t>Profession exercée : de santé (professionSante) TRE G15, du social (professionSocial) TRE R94, à usage de titre professionnel (usagerTitre) TRE R95, ou autre profession (autreProfession) TRE R291</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J106-EnsembleProfession-RASS/FHIR/JDV-J106-EnsembleProfession-RASS</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.start</t>
+    <t>Practitioner.qualification:exercicePro.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.period.end</t>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
   </si>
   <si>
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.issuer</t>
+    <t>Practitioner.qualification:exercicePro.issuer</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire</t>
@@ -3935,7 +3933,7 @@
   <dimension ref="A1:AJ650"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="70.33984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="70.953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.75" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="32.2578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -31930,7 +31928,7 @@
         <v>74</v>
       </c>
       <c r="G273" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H273" t="s" s="2">
         <v>73</v>
@@ -32754,7 +32752,7 @@
         <v>74</v>
       </c>
       <c r="G281" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H281" t="s" s="2">
         <v>73</v>
@@ -33578,7 +33576,7 @@
         <v>74</v>
       </c>
       <c r="G289" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H289" t="s" s="2">
         <v>73</v>
@@ -34402,7 +34400,7 @@
         <v>74</v>
       </c>
       <c r="G297" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H297" t="s" s="2">
         <v>73</v>
@@ -35226,7 +35224,7 @@
         <v>74</v>
       </c>
       <c r="G305" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H305" t="s" s="2">
         <v>73</v>
@@ -36050,7 +36048,7 @@
         <v>74</v>
       </c>
       <c r="G313" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H313" t="s" s="2">
         <v>73</v>
@@ -36874,7 +36872,7 @@
         <v>74</v>
       </c>
       <c r="G321" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H321" t="s" s="2">
         <v>73</v>
@@ -37698,7 +37696,7 @@
         <v>74</v>
       </c>
       <c r="G329" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H329" t="s" s="2">
         <v>73</v>
@@ -38522,7 +38520,7 @@
         <v>74</v>
       </c>
       <c r="G337" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H337" t="s" s="2">
         <v>73</v>
@@ -39346,7 +39344,7 @@
         <v>74</v>
       </c>
       <c r="G345" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H345" t="s" s="2">
         <v>73</v>
@@ -40170,7 +40168,7 @@
         <v>74</v>
       </c>
       <c r="G353" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H353" t="s" s="2">
         <v>73</v>
@@ -40994,7 +40992,7 @@
         <v>74</v>
       </c>
       <c r="G361" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H361" t="s" s="2">
         <v>73</v>
@@ -41818,7 +41816,7 @@
         <v>74</v>
       </c>
       <c r="G369" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H369" t="s" s="2">
         <v>73</v>
@@ -42642,7 +42640,7 @@
         <v>74</v>
       </c>
       <c r="G377" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H377" t="s" s="2">
         <v>73</v>
@@ -45308,7 +45306,7 @@
         <v>74</v>
       </c>
       <c r="G403" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H403" t="s" s="2">
         <v>73</v>
@@ -46132,7 +46130,7 @@
         <v>74</v>
       </c>
       <c r="G411" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H411" t="s" s="2">
         <v>73</v>
@@ -46956,7 +46954,7 @@
         <v>74</v>
       </c>
       <c r="G419" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H419" t="s" s="2">
         <v>73</v>
@@ -47780,7 +47778,7 @@
         <v>74</v>
       </c>
       <c r="G427" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H427" t="s" s="2">
         <v>73</v>
@@ -48604,7 +48602,7 @@
         <v>74</v>
       </c>
       <c r="G435" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H435" t="s" s="2">
         <v>73</v>
@@ -49428,7 +49426,7 @@
         <v>74</v>
       </c>
       <c r="G443" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H443" t="s" s="2">
         <v>73</v>
@@ -50252,7 +50250,7 @@
         <v>74</v>
       </c>
       <c r="G451" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H451" t="s" s="2">
         <v>73</v>
@@ -51076,7 +51074,7 @@
         <v>74</v>
       </c>
       <c r="G459" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H459" t="s" s="2">
         <v>73</v>
@@ -51900,7 +51898,7 @@
         <v>74</v>
       </c>
       <c r="G467" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H467" t="s" s="2">
         <v>73</v>
@@ -52724,7 +52722,7 @@
         <v>74</v>
       </c>
       <c r="G475" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H475" t="s" s="2">
         <v>73</v>
@@ -53548,7 +53546,7 @@
         <v>74</v>
       </c>
       <c r="G483" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H483" t="s" s="2">
         <v>73</v>
@@ -54372,7 +54370,7 @@
         <v>74</v>
       </c>
       <c r="G491" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H491" t="s" s="2">
         <v>73</v>
@@ -55196,7 +55194,7 @@
         <v>74</v>
       </c>
       <c r="G499" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H499" t="s" s="2">
         <v>73</v>
@@ -56020,7 +56018,7 @@
         <v>74</v>
       </c>
       <c r="G507" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H507" t="s" s="2">
         <v>73</v>
@@ -56938,7 +56936,7 @@
         <v>561</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>893</v>
+        <v>1020</v>
       </c>
       <c r="D516" t="s" s="2">
         <v>73</v>
@@ -56963,7 +56961,7 @@
         <v>140</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M516" t="s" s="2">
         <v>243</v>
@@ -57001,7 +56999,7 @@
       </c>
       <c r="Y516" s="2"/>
       <c r="Z516" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="AA516" t="s" s="2">
         <v>73</v>
@@ -57036,7 +57034,7 @@
     </row>
     <row r="517" hidden="true">
       <c r="A517" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B517" t="s" s="2">
         <v>725</v>
@@ -57140,7 +57138,7 @@
     </row>
     <row r="518" hidden="true">
       <c r="A518" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B518" t="s" s="2">
         <v>726</v>
@@ -57244,7 +57242,7 @@
     </row>
     <row r="519" hidden="true">
       <c r="A519" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B519" t="s" s="2">
         <v>871</v>
@@ -57344,7 +57342,7 @@
     </row>
     <row r="520" hidden="true">
       <c r="A520" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B520" t="s" s="2">
         <v>873</v>
@@ -57446,7 +57444,7 @@
     </row>
     <row r="521" hidden="true">
       <c r="A521" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B521" t="s" s="2">
         <v>875</v>
@@ -57475,7 +57473,7 @@
         <v>876</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M521" t="s" s="2">
         <v>878</v>
@@ -57548,7 +57546,7 @@
     </row>
     <row r="522" hidden="true">
       <c r="A522" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B522" t="s" s="2">
         <v>883</v>
@@ -57577,7 +57575,7 @@
         <v>876</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="M522" t="s" s="2">
         <v>885</v>
@@ -57652,7 +57650,7 @@
     </row>
     <row r="523" hidden="true">
       <c r="A523" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B523" t="s" s="2">
         <v>730</v>
@@ -57754,13 +57752,13 @@
     </row>
     <row r="524" hidden="true">
       <c r="A524" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B524" t="s" s="2">
         <v>537</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D524" t="s" s="2">
         <v>73</v>
@@ -57785,7 +57783,7 @@
         <v>538</v>
       </c>
       <c r="L524" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="M524" t="s" s="2">
         <v>540</v>
@@ -57856,7 +57854,7 @@
     </row>
     <row r="525" hidden="true">
       <c r="A525" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B525" t="s" s="2">
         <v>542</v>
@@ -57956,7 +57954,7 @@
     </row>
     <row r="526" hidden="true">
       <c r="A526" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B526" t="s" s="2">
         <v>543</v>
@@ -58058,7 +58056,7 @@
     </row>
     <row r="527" hidden="true">
       <c r="A527" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B527" t="s" s="2">
         <v>544</v>
@@ -58162,7 +58160,7 @@
     </row>
     <row r="528" hidden="true">
       <c r="A528" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B528" t="s" s="2">
         <v>549</v>
@@ -58264,7 +58262,7 @@
     </row>
     <row r="529" hidden="true">
       <c r="A529" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B529" t="s" s="2">
         <v>553</v>
@@ -58366,7 +58364,7 @@
     </row>
     <row r="530" hidden="true">
       <c r="A530" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B530" t="s" s="2">
         <v>559</v>
@@ -58466,7 +58464,7 @@
     </row>
     <row r="531" hidden="true">
       <c r="A531" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B531" t="s" s="2">
         <v>560</v>
@@ -58568,7 +58566,7 @@
     </row>
     <row r="532" hidden="true">
       <c r="A532" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B532" t="s" s="2">
         <v>561</v>
@@ -58670,7 +58668,7 @@
     </row>
     <row r="533" hidden="true">
       <c r="A533" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B533" t="s" s="2">
         <v>561</v>
@@ -58686,7 +58684,7 @@
         <v>74</v>
       </c>
       <c r="G533" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H533" t="s" s="2">
         <v>73</v>
@@ -58774,7 +58772,7 @@
     </row>
     <row r="534" hidden="true">
       <c r="A534" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B534" t="s" s="2">
         <v>567</v>
@@ -58874,7 +58872,7 @@
     </row>
     <row r="535" hidden="true">
       <c r="A535" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B535" t="s" s="2">
         <v>569</v>
@@ -58976,7 +58974,7 @@
     </row>
     <row r="536" hidden="true">
       <c r="A536" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B536" t="s" s="2">
         <v>571</v>
@@ -59080,7 +59078,7 @@
     </row>
     <row r="537" hidden="true">
       <c r="A537" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B537" t="s" s="2">
         <v>575</v>
@@ -59182,7 +59180,7 @@
     </row>
     <row r="538" hidden="true">
       <c r="A538" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B538" t="s" s="2">
         <v>577</v>
@@ -59286,7 +59284,7 @@
     </row>
     <row r="539" hidden="true">
       <c r="A539" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B539" t="s" s="2">
         <v>579</v>
@@ -59390,7 +59388,7 @@
     </row>
     <row r="540" hidden="true">
       <c r="A540" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>581</v>
@@ -59494,7 +59492,7 @@
     </row>
     <row r="541" hidden="true">
       <c r="A541" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B541" t="s" s="2">
         <v>561</v>
@@ -59510,7 +59508,7 @@
         <v>74</v>
       </c>
       <c r="G541" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H541" t="s" s="2">
         <v>73</v>
@@ -59598,7 +59596,7 @@
     </row>
     <row r="542" hidden="true">
       <c r="A542" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B542" t="s" s="2">
         <v>567</v>
@@ -59698,7 +59696,7 @@
     </row>
     <row r="543" hidden="true">
       <c r="A543" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B543" t="s" s="2">
         <v>569</v>
@@ -59800,7 +59798,7 @@
     </row>
     <row r="544" hidden="true">
       <c r="A544" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B544" t="s" s="2">
         <v>571</v>
@@ -59904,7 +59902,7 @@
     </row>
     <row r="545" hidden="true">
       <c r="A545" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B545" t="s" s="2">
         <v>575</v>
@@ -60006,7 +60004,7 @@
     </row>
     <row r="546" hidden="true">
       <c r="A546" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B546" t="s" s="2">
         <v>577</v>
@@ -60110,7 +60108,7 @@
     </row>
     <row r="547" hidden="true">
       <c r="A547" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B547" t="s" s="2">
         <v>579</v>
@@ -60214,7 +60212,7 @@
     </row>
     <row r="548" hidden="true">
       <c r="A548" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B548" t="s" s="2">
         <v>581</v>
@@ -60318,7 +60316,7 @@
     </row>
     <row r="549" hidden="true">
       <c r="A549" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B549" t="s" s="2">
         <v>561</v>
@@ -60334,7 +60332,7 @@
         <v>74</v>
       </c>
       <c r="G549" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H549" t="s" s="2">
         <v>73</v>
@@ -60422,7 +60420,7 @@
     </row>
     <row r="550" hidden="true">
       <c r="A550" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B550" t="s" s="2">
         <v>567</v>
@@ -60522,7 +60520,7 @@
     </row>
     <row r="551" hidden="true">
       <c r="A551" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B551" t="s" s="2">
         <v>569</v>
@@ -60624,7 +60622,7 @@
     </row>
     <row r="552" hidden="true">
       <c r="A552" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B552" t="s" s="2">
         <v>571</v>
@@ -60728,7 +60726,7 @@
     </row>
     <row r="553" hidden="true">
       <c r="A553" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B553" t="s" s="2">
         <v>575</v>
@@ -60830,7 +60828,7 @@
     </row>
     <row r="554" hidden="true">
       <c r="A554" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B554" t="s" s="2">
         <v>577</v>
@@ -60934,7 +60932,7 @@
     </row>
     <row r="555" hidden="true">
       <c r="A555" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B555" t="s" s="2">
         <v>579</v>
@@ -61038,7 +61036,7 @@
     </row>
     <row r="556" hidden="true">
       <c r="A556" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B556" t="s" s="2">
         <v>581</v>
@@ -61142,7 +61140,7 @@
     </row>
     <row r="557" hidden="true">
       <c r="A557" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B557" t="s" s="2">
         <v>561</v>
@@ -61158,7 +61156,7 @@
         <v>74</v>
       </c>
       <c r="G557" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H557" t="s" s="2">
         <v>73</v>
@@ -61246,7 +61244,7 @@
     </row>
     <row r="558" hidden="true">
       <c r="A558" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B558" t="s" s="2">
         <v>567</v>
@@ -61346,7 +61344,7 @@
     </row>
     <row r="559" hidden="true">
       <c r="A559" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B559" t="s" s="2">
         <v>569</v>
@@ -61448,7 +61446,7 @@
     </row>
     <row r="560" hidden="true">
       <c r="A560" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B560" t="s" s="2">
         <v>571</v>
@@ -61552,7 +61550,7 @@
     </row>
     <row r="561" hidden="true">
       <c r="A561" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B561" t="s" s="2">
         <v>575</v>
@@ -61654,7 +61652,7 @@
     </row>
     <row r="562" hidden="true">
       <c r="A562" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B562" t="s" s="2">
         <v>577</v>
@@ -61758,7 +61756,7 @@
     </row>
     <row r="563" hidden="true">
       <c r="A563" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B563" t="s" s="2">
         <v>579</v>
@@ -61862,7 +61860,7 @@
     </row>
     <row r="564" hidden="true">
       <c r="A564" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B564" t="s" s="2">
         <v>581</v>
@@ -61966,7 +61964,7 @@
     </row>
     <row r="565" hidden="true">
       <c r="A565" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B565" t="s" s="2">
         <v>561</v>
@@ -61982,7 +61980,7 @@
         <v>74</v>
       </c>
       <c r="G565" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H565" t="s" s="2">
         <v>73</v>
@@ -62070,7 +62068,7 @@
     </row>
     <row r="566" hidden="true">
       <c r="A566" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B566" t="s" s="2">
         <v>567</v>
@@ -62170,7 +62168,7 @@
     </row>
     <row r="567" hidden="true">
       <c r="A567" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B567" t="s" s="2">
         <v>569</v>
@@ -62272,7 +62270,7 @@
     </row>
     <row r="568" hidden="true">
       <c r="A568" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B568" t="s" s="2">
         <v>571</v>
@@ -62376,7 +62374,7 @@
     </row>
     <row r="569" hidden="true">
       <c r="A569" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B569" t="s" s="2">
         <v>575</v>
@@ -62478,7 +62476,7 @@
     </row>
     <row r="570" hidden="true">
       <c r="A570" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B570" t="s" s="2">
         <v>577</v>
@@ -62582,7 +62580,7 @@
     </row>
     <row r="571" hidden="true">
       <c r="A571" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B571" t="s" s="2">
         <v>579</v>
@@ -62686,7 +62684,7 @@
     </row>
     <row r="572" hidden="true">
       <c r="A572" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B572" t="s" s="2">
         <v>581</v>
@@ -62790,7 +62788,7 @@
     </row>
     <row r="573" hidden="true">
       <c r="A573" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B573" t="s" s="2">
         <v>561</v>
@@ -62806,7 +62804,7 @@
         <v>74</v>
       </c>
       <c r="G573" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H573" t="s" s="2">
         <v>73</v>
@@ -62894,7 +62892,7 @@
     </row>
     <row r="574" hidden="true">
       <c r="A574" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B574" t="s" s="2">
         <v>567</v>
@@ -62994,7 +62992,7 @@
     </row>
     <row r="575" hidden="true">
       <c r="A575" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B575" t="s" s="2">
         <v>569</v>
@@ -63096,7 +63094,7 @@
     </row>
     <row r="576" hidden="true">
       <c r="A576" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B576" t="s" s="2">
         <v>571</v>
@@ -63200,7 +63198,7 @@
     </row>
     <row r="577" hidden="true">
       <c r="A577" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B577" t="s" s="2">
         <v>575</v>
@@ -63302,7 +63300,7 @@
     </row>
     <row r="578" hidden="true">
       <c r="A578" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B578" t="s" s="2">
         <v>577</v>
@@ -63406,7 +63404,7 @@
     </row>
     <row r="579" hidden="true">
       <c r="A579" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B579" t="s" s="2">
         <v>579</v>
@@ -63510,7 +63508,7 @@
     </row>
     <row r="580" hidden="true">
       <c r="A580" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B580" t="s" s="2">
         <v>581</v>
@@ -63614,7 +63612,7 @@
     </row>
     <row r="581" hidden="true">
       <c r="A581" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B581" t="s" s="2">
         <v>561</v>
@@ -63630,7 +63628,7 @@
         <v>74</v>
       </c>
       <c r="G581" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H581" t="s" s="2">
         <v>73</v>
@@ -63718,7 +63716,7 @@
     </row>
     <row r="582" hidden="true">
       <c r="A582" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B582" t="s" s="2">
         <v>567</v>
@@ -63818,7 +63816,7 @@
     </row>
     <row r="583" hidden="true">
       <c r="A583" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B583" t="s" s="2">
         <v>569</v>
@@ -63920,7 +63918,7 @@
     </row>
     <row r="584" hidden="true">
       <c r="A584" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B584" t="s" s="2">
         <v>571</v>
@@ -64024,7 +64022,7 @@
     </row>
     <row r="585" hidden="true">
       <c r="A585" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B585" t="s" s="2">
         <v>575</v>
@@ -64126,7 +64124,7 @@
     </row>
     <row r="586" hidden="true">
       <c r="A586" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B586" t="s" s="2">
         <v>577</v>
@@ -64230,7 +64228,7 @@
     </row>
     <row r="587" hidden="true">
       <c r="A587" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B587" t="s" s="2">
         <v>579</v>
@@ -64334,7 +64332,7 @@
     </row>
     <row r="588" hidden="true">
       <c r="A588" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B588" t="s" s="2">
         <v>581</v>
@@ -64438,7 +64436,7 @@
     </row>
     <row r="589" hidden="true">
       <c r="A589" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B589" t="s" s="2">
         <v>561</v>
@@ -64454,7 +64452,7 @@
         <v>74</v>
       </c>
       <c r="G589" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H589" t="s" s="2">
         <v>73</v>
@@ -64542,7 +64540,7 @@
     </row>
     <row r="590" hidden="true">
       <c r="A590" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B590" t="s" s="2">
         <v>567</v>
@@ -64642,7 +64640,7 @@
     </row>
     <row r="591" hidden="true">
       <c r="A591" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B591" t="s" s="2">
         <v>569</v>
@@ -64744,7 +64742,7 @@
     </row>
     <row r="592" hidden="true">
       <c r="A592" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B592" t="s" s="2">
         <v>571</v>
@@ -64848,7 +64846,7 @@
     </row>
     <row r="593" hidden="true">
       <c r="A593" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B593" t="s" s="2">
         <v>575</v>
@@ -64950,7 +64948,7 @@
     </row>
     <row r="594" hidden="true">
       <c r="A594" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B594" t="s" s="2">
         <v>577</v>
@@ -65054,7 +65052,7 @@
     </row>
     <row r="595" hidden="true">
       <c r="A595" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B595" t="s" s="2">
         <v>579</v>
@@ -65158,7 +65156,7 @@
     </row>
     <row r="596" hidden="true">
       <c r="A596" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B596" t="s" s="2">
         <v>581</v>
@@ -65262,7 +65260,7 @@
     </row>
     <row r="597" hidden="true">
       <c r="A597" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B597" t="s" s="2">
         <v>561</v>
@@ -65278,7 +65276,7 @@
         <v>74</v>
       </c>
       <c r="G597" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H597" t="s" s="2">
         <v>73</v>
@@ -65366,7 +65364,7 @@
     </row>
     <row r="598" hidden="true">
       <c r="A598" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B598" t="s" s="2">
         <v>567</v>
@@ -65466,7 +65464,7 @@
     </row>
     <row r="599" hidden="true">
       <c r="A599" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B599" t="s" s="2">
         <v>569</v>
@@ -65568,7 +65566,7 @@
     </row>
     <row r="600" hidden="true">
       <c r="A600" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B600" t="s" s="2">
         <v>571</v>
@@ -65672,7 +65670,7 @@
     </row>
     <row r="601" hidden="true">
       <c r="A601" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B601" t="s" s="2">
         <v>575</v>
@@ -65774,7 +65772,7 @@
     </row>
     <row r="602" hidden="true">
       <c r="A602" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B602" t="s" s="2">
         <v>577</v>
@@ -65878,7 +65876,7 @@
     </row>
     <row r="603" hidden="true">
       <c r="A603" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B603" t="s" s="2">
         <v>579</v>
@@ -65982,7 +65980,7 @@
     </row>
     <row r="604" hidden="true">
       <c r="A604" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B604" t="s" s="2">
         <v>581</v>
@@ -66086,7 +66084,7 @@
     </row>
     <row r="605" hidden="true">
       <c r="A605" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B605" t="s" s="2">
         <v>561</v>
@@ -66102,7 +66100,7 @@
         <v>74</v>
       </c>
       <c r="G605" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H605" t="s" s="2">
         <v>73</v>
@@ -66190,7 +66188,7 @@
     </row>
     <row r="606" hidden="true">
       <c r="A606" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B606" t="s" s="2">
         <v>567</v>
@@ -66290,7 +66288,7 @@
     </row>
     <row r="607" hidden="true">
       <c r="A607" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B607" t="s" s="2">
         <v>569</v>
@@ -66392,7 +66390,7 @@
     </row>
     <row r="608" hidden="true">
       <c r="A608" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B608" t="s" s="2">
         <v>571</v>
@@ -66496,7 +66494,7 @@
     </row>
     <row r="609" hidden="true">
       <c r="A609" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B609" t="s" s="2">
         <v>575</v>
@@ -66598,7 +66596,7 @@
     </row>
     <row r="610" hidden="true">
       <c r="A610" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B610" t="s" s="2">
         <v>577</v>
@@ -66702,7 +66700,7 @@
     </row>
     <row r="611" hidden="true">
       <c r="A611" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B611" t="s" s="2">
         <v>579</v>
@@ -66806,7 +66804,7 @@
     </row>
     <row r="612" hidden="true">
       <c r="A612" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B612" t="s" s="2">
         <v>581</v>
@@ -66910,7 +66908,7 @@
     </row>
     <row r="613" hidden="true">
       <c r="A613" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B613" t="s" s="2">
         <v>561</v>
@@ -66926,7 +66924,7 @@
         <v>74</v>
       </c>
       <c r="G613" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H613" t="s" s="2">
         <v>73</v>
@@ -67014,7 +67012,7 @@
     </row>
     <row r="614" hidden="true">
       <c r="A614" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B614" t="s" s="2">
         <v>567</v>
@@ -67114,7 +67112,7 @@
     </row>
     <row r="615" hidden="true">
       <c r="A615" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B615" t="s" s="2">
         <v>569</v>
@@ -67216,7 +67214,7 @@
     </row>
     <row r="616" hidden="true">
       <c r="A616" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B616" t="s" s="2">
         <v>571</v>
@@ -67320,7 +67318,7 @@
     </row>
     <row r="617" hidden="true">
       <c r="A617" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B617" t="s" s="2">
         <v>575</v>
@@ -67422,7 +67420,7 @@
     </row>
     <row r="618" hidden="true">
       <c r="A618" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B618" t="s" s="2">
         <v>577</v>
@@ -67526,7 +67524,7 @@
     </row>
     <row r="619" hidden="true">
       <c r="A619" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B619" t="s" s="2">
         <v>579</v>
@@ -67630,7 +67628,7 @@
     </row>
     <row r="620" hidden="true">
       <c r="A620" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B620" t="s" s="2">
         <v>581</v>
@@ -67734,7 +67732,7 @@
     </row>
     <row r="621" hidden="true">
       <c r="A621" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B621" t="s" s="2">
         <v>561</v>
@@ -67750,7 +67748,7 @@
         <v>74</v>
       </c>
       <c r="G621" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H621" t="s" s="2">
         <v>73</v>
@@ -67838,7 +67836,7 @@
     </row>
     <row r="622" hidden="true">
       <c r="A622" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B622" t="s" s="2">
         <v>567</v>
@@ -67938,7 +67936,7 @@
     </row>
     <row r="623" hidden="true">
       <c r="A623" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B623" t="s" s="2">
         <v>569</v>
@@ -68040,7 +68038,7 @@
     </row>
     <row r="624" hidden="true">
       <c r="A624" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B624" t="s" s="2">
         <v>571</v>
@@ -68144,7 +68142,7 @@
     </row>
     <row r="625" hidden="true">
       <c r="A625" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B625" t="s" s="2">
         <v>575</v>
@@ -68246,7 +68244,7 @@
     </row>
     <row r="626" hidden="true">
       <c r="A626" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B626" t="s" s="2">
         <v>577</v>
@@ -68350,7 +68348,7 @@
     </row>
     <row r="627" hidden="true">
       <c r="A627" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B627" t="s" s="2">
         <v>579</v>
@@ -68454,7 +68452,7 @@
     </row>
     <row r="628" hidden="true">
       <c r="A628" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B628" t="s" s="2">
         <v>581</v>
@@ -68558,7 +68556,7 @@
     </row>
     <row r="629" hidden="true">
       <c r="A629" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B629" t="s" s="2">
         <v>561</v>
@@ -68574,7 +68572,7 @@
         <v>74</v>
       </c>
       <c r="G629" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H629" t="s" s="2">
         <v>73</v>
@@ -68662,7 +68660,7 @@
     </row>
     <row r="630" hidden="true">
       <c r="A630" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B630" t="s" s="2">
         <v>567</v>
@@ -68762,7 +68760,7 @@
     </row>
     <row r="631" hidden="true">
       <c r="A631" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B631" t="s" s="2">
         <v>569</v>
@@ -68864,7 +68862,7 @@
     </row>
     <row r="632" hidden="true">
       <c r="A632" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B632" t="s" s="2">
         <v>571</v>
@@ -68968,7 +68966,7 @@
     </row>
     <row r="633" hidden="true">
       <c r="A633" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B633" t="s" s="2">
         <v>575</v>
@@ -69070,7 +69068,7 @@
     </row>
     <row r="634" hidden="true">
       <c r="A634" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B634" t="s" s="2">
         <v>577</v>
@@ -69174,7 +69172,7 @@
     </row>
     <row r="635" hidden="true">
       <c r="A635" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B635" t="s" s="2">
         <v>579</v>
@@ -69278,7 +69276,7 @@
     </row>
     <row r="636" hidden="true">
       <c r="A636" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B636" t="s" s="2">
         <v>581</v>
@@ -69382,7 +69380,7 @@
     </row>
     <row r="637" hidden="true">
       <c r="A637" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B637" t="s" s="2">
         <v>561</v>
@@ -69398,7 +69396,7 @@
         <v>74</v>
       </c>
       <c r="G637" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H637" t="s" s="2">
         <v>73</v>
@@ -69486,7 +69484,7 @@
     </row>
     <row r="638" hidden="true">
       <c r="A638" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B638" t="s" s="2">
         <v>567</v>
@@ -69586,7 +69584,7 @@
     </row>
     <row r="639" hidden="true">
       <c r="A639" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B639" t="s" s="2">
         <v>569</v>
@@ -69688,7 +69686,7 @@
     </row>
     <row r="640" hidden="true">
       <c r="A640" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B640" t="s" s="2">
         <v>571</v>
@@ -69792,7 +69790,7 @@
     </row>
     <row r="641" hidden="true">
       <c r="A641" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B641" t="s" s="2">
         <v>575</v>
@@ -69894,7 +69892,7 @@
     </row>
     <row r="642" hidden="true">
       <c r="A642" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B642" t="s" s="2">
         <v>577</v>
@@ -69998,7 +69996,7 @@
     </row>
     <row r="643" hidden="true">
       <c r="A643" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B643" t="s" s="2">
         <v>579</v>
@@ -70102,7 +70100,7 @@
     </row>
     <row r="644" hidden="true">
       <c r="A644" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B644" t="s" s="2">
         <v>581</v>
@@ -70206,13 +70204,13 @@
     </row>
     <row r="645" hidden="true">
       <c r="A645" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B645" t="s" s="2">
         <v>561</v>
       </c>
       <c r="C645" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D645" t="s" s="2">
         <v>73</v>
@@ -70237,7 +70235,7 @@
         <v>140</v>
       </c>
       <c r="L645" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="M645" t="s" s="2">
         <v>243</v>
@@ -70275,7 +70273,7 @@
       </c>
       <c r="Y645" s="2"/>
       <c r="Z645" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="AA645" t="s" s="2">
         <v>73</v>
@@ -70310,13 +70308,13 @@
     </row>
     <row r="646" hidden="true">
       <c r="A646" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B646" t="s" s="2">
         <v>561</v>
       </c>
       <c r="C646" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="D646" t="s" s="2">
         <v>73</v>
@@ -70341,7 +70339,7 @@
         <v>140</v>
       </c>
       <c r="L646" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="M646" t="s" s="2">
         <v>243</v>
@@ -70379,7 +70377,7 @@
       </c>
       <c r="Y646" s="2"/>
       <c r="Z646" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AA646" t="s" s="2">
         <v>73</v>
@@ -70414,7 +70412,7 @@
     </row>
     <row r="647" hidden="true">
       <c r="A647" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B647" t="s" s="2">
         <v>725</v>
@@ -70518,7 +70516,7 @@
     </row>
     <row r="648" hidden="true">
       <c r="A648" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B648" t="s" s="2">
         <v>726</v>
@@ -70622,7 +70620,7 @@
     </row>
     <row r="649" hidden="true">
       <c r="A649" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B649" t="s" s="2">
         <v>730</v>
@@ -70724,10 +70722,10 @@
     </row>
     <row r="650" hidden="true">
       <c r="A650" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B650" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C650" s="2"/>
       <c r="D650" t="s" s="2">
@@ -70750,19 +70748,19 @@
         <v>73</v>
       </c>
       <c r="K650" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="L650" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="M650" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N650" t="s" s="2">
         <v>556</v>
       </c>
       <c r="O650" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="P650" t="s" s="2">
         <v>73</v>
@@ -70791,7 +70789,7 @@
       </c>
       <c r="Y650" s="2"/>
       <c r="Z650" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="AA650" t="s" s="2">
         <v>73</v>
@@ -70809,7 +70807,7 @@
         <v>73</v>
       </c>
       <c r="AF650" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="AG650" t="s" s="2">
         <v>74</v>

--- a/ig/nr-corrections/StructureDefinition-as-practitioner.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:26:19+00:00</t>
+    <t>2024-02-12T14:49:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-corrections/StructureDefinition-as-practitioner.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:49:01+00:00</t>
+    <t>2024-02-16T11:05:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,7 +745,8 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1015,8 +1016,7 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+    <t>Description of identifier</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -2783,7 +2783,7 @@
     <t>exercicePro</t>
   </si>
   <si>
-    <t>profession : exercice professionnel ou future profession de l'étudiant et la catégorie de profession.</t>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.id</t>
@@ -10867,7 +10867,7 @@
         <v>231</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>233</v>
@@ -12921,7 +12921,7 @@
         <v>231</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>233</v>
